--- a/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_supbrut_a_2021_los_lagos.xlsx
+++ b/output/graficos_regionales_correlaciones/plot_regional_correl_matriz_e_supbrut_a_2021_los_lagos.xlsx
@@ -114,7 +114,7 @@
     <t xml:space="preserve">Fecha de creación</t>
   </si>
   <si>
-    <t xml:space="preserve">2026-09-18 14:26</t>
+    <t xml:space="preserve">2026-09-24 01:16</t>
   </si>
   <si>
     <t xml:space="preserve">Fuente</t>
@@ -736,13 +736,13 @@
         <v>30</v>
       </c>
       <c r="E10" s="2" t="n">
-        <v>-0.29</v>
+        <v>-0.33</v>
       </c>
       <c r="F10" s="2" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G10" s="2" t="n">
-        <v>0.07</v>
+        <v>0.11</v>
       </c>
     </row>
     <row r="11">
@@ -759,13 +759,13 @@
         <v>30</v>
       </c>
       <c r="E11" s="2" t="n">
-        <v>-0.17</v>
+        <v>-0.26</v>
       </c>
       <c r="F11" s="2" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G11" s="2" t="n">
-        <v>0.44</v>
+        <v>0.54</v>
       </c>
     </row>
     <row r="12">
@@ -785,7 +785,7 @@
         <v>-0.22</v>
       </c>
       <c r="F12" s="2" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G12" s="2" t="n">
         <v>-0.07</v>
@@ -805,13 +805,13 @@
         <v>30</v>
       </c>
       <c r="E13" s="2" t="n">
-        <v>-0.11</v>
+        <v>-0.09</v>
       </c>
       <c r="F13" s="2" t="n">
-        <v>322</v>
+        <v>325</v>
       </c>
       <c r="G13" s="2" t="n">
-        <v>-0.23</v>
+        <v>-0.26</v>
       </c>
     </row>
     <row r="14">
@@ -851,13 +851,13 @@
         <v>30</v>
       </c>
       <c r="E15" s="2" t="n">
-        <v>-0.15</v>
+        <v>-0.84</v>
       </c>
       <c r="F15" s="2" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G15" s="2" t="n">
-        <v>-0.08</v>
+        <v>0.61</v>
       </c>
     </row>
     <row r="16">
@@ -874,13 +874,13 @@
         <v>30</v>
       </c>
       <c r="E16" s="2" t="n">
-        <v>0.05</v>
+        <v>0.72</v>
       </c>
       <c r="F16" s="2" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G16" s="2" t="n">
-        <v>-0.03</v>
+        <v>-0.7</v>
       </c>
     </row>
     <row r="17">
@@ -897,13 +897,13 @@
         <v>30</v>
       </c>
       <c r="E17" s="2" t="n">
-        <v>0.02</v>
+        <v>0.01</v>
       </c>
       <c r="F17" s="2" t="n">
-        <v>324</v>
+        <v>325</v>
       </c>
       <c r="G17" s="2" t="n">
-        <v>0.07</v>
+        <v>0.09</v>
       </c>
     </row>
     <row r="18">
